--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run7/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run7/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.4300,0.3371,0.1793,0.1845</t>
-  </si>
-  <si>
-    <t>0.0087,0.0023,0.0008,0.9957</t>
-  </si>
-  <si>
-    <t>0.6523,0.0299,0.0014,0.2935</t>
-  </si>
-  <si>
-    <t>0.1660,0.0008,0.0002,0.9577</t>
-  </si>
-  <si>
-    <t>0.9949,0.0011,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9975,0.0003,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9801,0.0191,0.0046,0.0007</t>
-  </si>
-  <si>
-    <t>0.9895,0.0012,0.0011,0.0031</t>
-  </si>
-  <si>
-    <t>0.9817,0.0199,0.0024,0.0005</t>
-  </si>
-  <si>
-    <t>0.9901,0.0034,0.0002,0.0012</t>
-  </si>
-  <si>
-    <t>0.9951,0.0009,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9952,0.0002,0.0000,0.0023</t>
-  </si>
-  <si>
-    <t>0.3605,0.1000,0.5796,0.0107</t>
-  </si>
-  <si>
-    <t>0.3876,0.0450,0.6489,0.0062</t>
-  </si>
-  <si>
-    <t>0.1716,0.0191,0.8614,0.0003</t>
-  </si>
-  <si>
-    <t>0.1909,0.0123,0.8514,0.0021</t>
-  </si>
-  <si>
-    <t>0.7178,0.0109,0.4289,0.0056</t>
-  </si>
-  <si>
-    <t>0.0247,0.9735,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.0594,0.9615,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.3778,0.7254,0.0107,0.0019</t>
-  </si>
-  <si>
-    <t>0.2470,0.8300,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.0087,0.9846,0.0007,0.0010</t>
-  </si>
-  <si>
-    <t>0.1088,0.0370,0.8002,0.1037</t>
-  </si>
-  <si>
-    <t>0.6171,0.0193,0.3771,0.0340</t>
-  </si>
-  <si>
-    <t>0.0241,0.0046,0.9804,0.0010</t>
-  </si>
-  <si>
-    <t>0.3122,0.0497,0.6326,0.0101</t>
-  </si>
-  <si>
-    <t>0.1513,0.0135,0.8821,0.0045</t>
-  </si>
-  <si>
-    <t>0.0459,0.0083,0.9002,0.0483</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.9968,0.0016</t>
-  </si>
-  <si>
-    <t>0.5703,0.6307,0.0046,0.0011</t>
-  </si>
-  <si>
-    <t>0.4030,0.5044,0.2019,0.0146</t>
-  </si>
-  <si>
-    <t>0.0058,0.0078,0.9789,0.0073</t>
-  </si>
-  <si>
-    <t>0.0472,0.8447,0.1412,0.0044</t>
-  </si>
-  <si>
-    <t>0.6942,0.1469,0.0022,0.0683</t>
-  </si>
-  <si>
-    <t>0.6157,0.4177,0.0326,0.0117</t>
-  </si>
-  <si>
-    <t>0.7962,0.2775,0.0090,0.0031</t>
-  </si>
-  <si>
-    <t>0.0104,0.9718,0.0876,0.0018</t>
-  </si>
-  <si>
-    <t>0.0429,0.7856,0.1310,0.0922</t>
-  </si>
-  <si>
-    <t>0.0879,0.0613,0.9003,0.0130</t>
-  </si>
-  <si>
-    <t>0.0594,0.1272,0.7928,0.0280</t>
-  </si>
-  <si>
-    <t>0.0318,0.0212,0.7814,0.2631</t>
-  </si>
-  <si>
-    <t>0.0579,0.0996,0.8933,0.0032</t>
-  </si>
-  <si>
-    <t>0.0024,0.9860,0.0104,0.0002</t>
-  </si>
-  <si>
-    <t>0.0782,0.0221,0.9312,0.0039</t>
-  </si>
-  <si>
-    <t>0.0016,0.9451,0.0011,0.6456</t>
-  </si>
-  <si>
-    <t>0.0026,0.9643,0.0188,0.1006</t>
-  </si>
-  <si>
-    <t>0.0048,0.9706,0.0964,0.0007</t>
-  </si>
-  <si>
-    <t>0.0023,0.9735,0.1518,0.0041</t>
-  </si>
-  <si>
-    <t>0.0105,0.3130,0.9427,0.0042</t>
-  </si>
-  <si>
-    <t>0.0005,0.2041,0.9898,0.0005</t>
-  </si>
-  <si>
-    <t>0.1117,0.0292,0.8759,0.0023</t>
-  </si>
-  <si>
-    <t>0.0149,0.0022,0.9878,0.0007</t>
-  </si>
-  <si>
-    <t>0.0057,0.0024,0.9873,0.0031</t>
-  </si>
-  <si>
-    <t>0.0050,0.0530,0.9737,0.0027</t>
-  </si>
-  <si>
-    <t>0.9583,0.0390,0.0051,0.0016</t>
-  </si>
-  <si>
-    <t>0.9849,0.0052,0.0008,0.0020</t>
-  </si>
-  <si>
-    <t>0.9611,0.0147,0.0009,0.0078</t>
-  </si>
-  <si>
-    <t>0.0007,0.0202,0.9918,0.0056</t>
-  </si>
-  <si>
-    <t>0.9554,0.0160,0.0059,0.0103</t>
-  </si>
-  <si>
-    <t>0.9901,0.0087,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.8665,0.1548,0.0030,0.0048</t>
-  </si>
-  <si>
-    <t>0.0034,0.4461,0.9686,0.0019</t>
-  </si>
-  <si>
-    <t>0.0009,0.0015,0.9850,0.0139</t>
-  </si>
-  <si>
-    <t>0.0472,0.0063,0.9586,0.0030</t>
-  </si>
-  <si>
-    <t>0.0007,0.8713,0.9755,0.0001</t>
-  </si>
-  <si>
-    <t>0.0045,0.0091,0.9864,0.0029</t>
-  </si>
-  <si>
-    <t>0.0232,0.4422,0.6852,0.0034</t>
-  </si>
-  <si>
-    <t>0.0359,0.9705,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.8688,0.0241,0.1473,0.0055</t>
-  </si>
-  <si>
-    <t>0.7160,0.0386,0.3750,0.0046</t>
-  </si>
-  <si>
-    <t>0.0035,0.0423,0.9843,0.0011</t>
-  </si>
-  <si>
-    <t>0.0007,0.7657,0.9514,0.0002</t>
-  </si>
-  <si>
-    <t>0.0050,0.8787,0.7962,0.0006</t>
-  </si>
-  <si>
-    <t>0.0075,0.9211,0.6063,0.0010</t>
-  </si>
-  <si>
-    <t>0.0002,0.9709,0.4519,0.0000</t>
-  </si>
-  <si>
-    <t>0.0158,0.0037,0.0536,0.9707</t>
-  </si>
-  <si>
-    <t>0.0017,0.0014,0.0010,0.9983</t>
-  </si>
-  <si>
-    <t>0.0219,0.0026,0.0011,0.9916</t>
-  </si>
-  <si>
-    <t>0.0049,0.0003,0.0008,0.9973</t>
-  </si>
-  <si>
-    <t>0.0235,0.0081,0.0067,0.9852</t>
-  </si>
-  <si>
-    <t>0.0028,0.0026,0.0002,0.9983</t>
-  </si>
-  <si>
-    <t>0.0019,0.9213,0.7776,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.8462,0.9419,0.0003</t>
-  </si>
-  <si>
-    <t>0.0144,0.3904,0.8522,0.0041</t>
-  </si>
-  <si>
-    <t>0.0102,0.2635,0.9621,0.0028</t>
-  </si>
-  <si>
-    <t>0.0063,0.8758,0.3634,0.0004</t>
-  </si>
-  <si>
-    <t>0.0046,0.6013,0.9179,0.0020</t>
-  </si>
-  <si>
-    <t>0.9940,0.0019,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9572,0.0555,0.0021,0.0010</t>
-  </si>
-  <si>
-    <t>0.9705,0.0314,0.0052,0.0006</t>
-  </si>
-  <si>
-    <t>0.9894,0.0042,0.0004,0.0013</t>
-  </si>
-  <si>
-    <t>0.9585,0.0375,0.0021,0.0017</t>
-  </si>
-  <si>
-    <t>0.9959,0.0008,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9845,0.0190,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.9858,0.0168,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.9960,0.0005,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9963,0.0007,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9931,0.0040,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9955,0.0019,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9948,0.0007,0.0000,0.0011</t>
-  </si>
-  <si>
-    <t>0.9953,0.0013,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9956,0.0006,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.9927,0.0011,0.0005,0.0012</t>
-  </si>
-  <si>
-    <t>0.0005,0.0061,0.9956,0.0019</t>
-  </si>
-  <si>
-    <t>0.1519,0.0628,0.7764,0.0015</t>
-  </si>
-  <si>
-    <t>0.7509,0.0063,0.1854,0.0327</t>
-  </si>
-  <si>
-    <t>0.0337,0.0133,0.9452,0.0075</t>
-  </si>
-  <si>
-    <t>0.1301,0.8634,0.0117,0.0067</t>
-  </si>
-  <si>
-    <t>0.0332,0.9573,0.0008,0.0033</t>
-  </si>
-  <si>
-    <t>0.1657,0.7818,0.0003,0.0064</t>
-  </si>
-  <si>
-    <t>0.3824,0.7940,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.0427,0.9419,0.0057,0.0072</t>
-  </si>
-  <si>
-    <t>0.1487,0.8706,0.0018,0.0011</t>
-  </si>
-  <si>
-    <t>0.6084,0.5287,0.0040,0.0025</t>
-  </si>
-  <si>
-    <t>0.7831,0.0550,0.0988,0.0303</t>
-  </si>
-  <si>
-    <t>0.3533,0.0126,0.7353,0.0147</t>
-  </si>
-  <si>
-    <t>0.6011,0.0971,0.2919,0.0124</t>
-  </si>
-  <si>
-    <t>0.4137,0.0368,0.6189,0.0198</t>
-  </si>
-  <si>
-    <t>0.0266,0.3481,0.0282,0.9214</t>
-  </si>
-  <si>
-    <t>0.0026,0.9896,0.0211,0.0007</t>
-  </si>
-  <si>
-    <t>0.0016,0.9829,0.0296,0.0256</t>
-  </si>
-  <si>
-    <t>0.0184,0.9598,0.0060,0.0239</t>
-  </si>
-  <si>
-    <t>0.0001,0.9418,0.9154,0.0001</t>
-  </si>
-  <si>
-    <t>0.0192,0.9736,0.0111,0.0008</t>
-  </si>
-  <si>
-    <t>0.7669,0.2417,0.0558,0.0110</t>
-  </si>
-  <si>
-    <t>0.3778,0.7116,0.0081,0.0058</t>
-  </si>
-  <si>
-    <t>0.9897,0.0033,0.0010,0.0016</t>
-  </si>
-  <si>
-    <t>0.9855,0.0072,0.0020,0.0012</t>
-  </si>
-  <si>
-    <t>0.9738,0.0045,0.0007,0.0080</t>
-  </si>
-  <si>
-    <t>0.9652,0.0109,0.0132,0.0044</t>
-  </si>
-  <si>
-    <t>0.9838,0.0069,0.0090,0.0007</t>
-  </si>
-  <si>
-    <t>0.9797,0.0119,0.0031,0.0023</t>
-  </si>
-  <si>
-    <t>0.9812,0.0031,0.0013,0.0046</t>
-  </si>
-  <si>
-    <t>0.9827,0.0058,0.0078,0.0013</t>
-  </si>
-  <si>
-    <t>0.0032,0.3013,0.9764,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.8231,0.9279,0.0001</t>
-  </si>
-  <si>
-    <t>0.0110,0.4035,0.8167,0.0022</t>
-  </si>
-  <si>
-    <t>0.0749,0.1091,0.8106,0.0084</t>
-  </si>
-  <si>
-    <t>0.7978,0.0517,0.1065,0.0236</t>
-  </si>
-  <si>
-    <t>0.6578,0.2035,0.1022,0.0252</t>
-  </si>
-  <si>
-    <t>0.7562,0.0009,0.4147,0.0052</t>
-  </si>
-  <si>
-    <t>0.5670,0.0715,0.4015,0.0072</t>
-  </si>
-  <si>
-    <t>0.0291,0.0019,0.0009,0.9900</t>
-  </si>
-  <si>
-    <t>0.0005,0.0058,0.0011,0.9990</t>
-  </si>
-  <si>
-    <t>0.0034,0.0054,0.0046,0.9962</t>
-  </si>
-  <si>
-    <t>0.0093,0.0013,0.0002,0.9967</t>
-  </si>
-  <si>
-    <t>0.0018,0.6065,0.9705,0.0004</t>
-  </si>
-  <si>
-    <t>0.9451,0.0484,0.0094,0.0025</t>
-  </si>
-  <si>
-    <t>0.2815,0.7619,0.0047,0.0061</t>
-  </si>
-  <si>
-    <t>0.9829,0.0043,0.0007,0.0029</t>
-  </si>
-  <si>
-    <t>0.7452,0.3031,0.0164,0.0010</t>
-  </si>
-  <si>
-    <t>0.9719,0.0040,0.0088,0.0038</t>
-  </si>
-  <si>
-    <t>0.6919,0.0103,0.0213,0.3302</t>
-  </si>
-  <si>
-    <t>0.9737,0.0043,0.0014,0.0090</t>
-  </si>
-  <si>
-    <t>0.0012,0.2604,0.9395,0.0328</t>
-  </si>
-  <si>
-    <t>0.8622,0.0005,0.0109,0.0771</t>
-  </si>
-  <si>
-    <t>0.8384,0.0025,0.0183,0.0887</t>
-  </si>
-  <si>
-    <t>0.8677,0.1178,0.0158,0.0042</t>
-  </si>
-  <si>
-    <t>0.9288,0.0398,0.0084,0.0045</t>
-  </si>
-  <si>
-    <t>0.8019,0.1658,0.0422,0.0220</t>
-  </si>
-  <si>
-    <t>0.1927,0.6050,0.1822,0.0180</t>
-  </si>
-  <si>
-    <t>0.9098,0.0664,0.0065,0.0050</t>
-  </si>
-  <si>
-    <t>0.8894,0.0825,0.0214,0.0085</t>
-  </si>
-  <si>
-    <t>0.9688,0.0008,0.0002,0.0317</t>
-  </si>
-  <si>
-    <t>0.9725,0.0058,0.0009,0.0089</t>
-  </si>
-  <si>
-    <t>0.9816,0.0057,0.0014,0.0028</t>
-  </si>
-  <si>
-    <t>0.9901,0.0026,0.0012,0.0015</t>
-  </si>
-  <si>
-    <t>0.9878,0.0006,0.0002,0.0069</t>
-  </si>
-  <si>
-    <t>0.9760,0.0130,0.0102,0.0014</t>
-  </si>
-  <si>
-    <t>0.9863,0.0071,0.0046,0.0006</t>
-  </si>
-  <si>
-    <t>0.9875,0.0025,0.0005,0.0034</t>
-  </si>
-  <si>
-    <t>0.6029,0.3767,0.0015,0.0108</t>
-  </si>
-  <si>
-    <t>0.8069,0.3016,0.0080,0.0013</t>
-  </si>
-  <si>
-    <t>0.7926,0.2593,0.0141,0.0042</t>
-  </si>
-  <si>
-    <t>0.7927,0.1611,0.0790,0.0091</t>
-  </si>
-  <si>
-    <t>0.8941,0.2262,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.8942,0.0586,0.0176,0.0107</t>
-  </si>
-  <si>
-    <t>0.9768,0.0316,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.8731,0.1155,0.0136,0.0141</t>
-  </si>
-  <si>
-    <t>0.0029,0.0175,0.9923,0.0012</t>
-  </si>
-  <si>
-    <t>0.9303,0.1041,0.0016,0.0008</t>
-  </si>
-  <si>
-    <t>0.0010,0.0030,0.9964,0.0005</t>
-  </si>
-  <si>
-    <t>0.0050,0.2102,0.9262,0.0174</t>
-  </si>
-  <si>
-    <t>0.1665,0.0441,0.8223,0.0048</t>
-  </si>
-  <si>
-    <t>0.0275,0.0147,0.9797,0.0005</t>
-  </si>
-  <si>
-    <t>0.0200,0.0950,0.9492,0.0015</t>
-  </si>
-  <si>
-    <t>0.0118,0.0008,0.9912,0.0003</t>
-  </si>
-  <si>
-    <t>0.0022,0.0128,0.9873,0.0035</t>
-  </si>
-  <si>
-    <t>0.2916,0.1082,0.6138,0.0191</t>
-  </si>
-  <si>
-    <t>0.2730,0.1156,0.5962,0.0197</t>
-  </si>
-  <si>
-    <t>0.5489,0.0061,0.6941,0.0033</t>
-  </si>
-  <si>
-    <t>0.3386,0.0238,0.7522,0.0010</t>
-  </si>
-  <si>
-    <t>0.1677,0.2501,0.4790,0.0013</t>
-  </si>
-  <si>
-    <t>0.4748,0.2698,0.2757,0.0782</t>
-  </si>
-  <si>
-    <t>0.5630,0.0855,0.3507,0.0634</t>
-  </si>
-  <si>
-    <t>0.6081,0.0741,0.4196,0.0151</t>
-  </si>
-  <si>
-    <t>0.3898,0.7448,0.0023,0.0013</t>
-  </si>
-  <si>
-    <t>0.8817,0.2355,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.8396,0.2260,0.0021,0.0033</t>
-  </si>
-  <si>
-    <t>0.9759,0.0196,0.0013,0.0014</t>
-  </si>
-  <si>
-    <t>0.2906,0.7597,0.0079,0.0037</t>
-  </si>
-  <si>
-    <t>0.4913,0.1807,0.3715,0.0488</t>
-  </si>
-  <si>
-    <t>0.7998,0.0078,0.2482,0.0138</t>
-  </si>
-  <si>
-    <t>0.7789,0.0122,0.1908,0.0165</t>
-  </si>
-  <si>
-    <t>0.6627,0.0185,0.4452,0.0070</t>
-  </si>
-  <si>
-    <t>0.6166,0.0226,0.3459,0.0694</t>
-  </si>
-  <si>
-    <t>0.0167,0.0127,0.9400,0.0539</t>
-  </si>
-  <si>
-    <t>0.0626,0.3872,0.6861,0.0593</t>
-  </si>
-  <si>
-    <t>0.0562,0.1587,0.8657,0.0108</t>
-  </si>
-  <si>
-    <t>0.0327,0.0151,0.7846,0.2409</t>
-  </si>
-  <si>
-    <t>0.0118,0.9298,0.0396,0.0021</t>
-  </si>
-  <si>
-    <t>0.9916,0.0005,0.0000,0.0028</t>
-  </si>
-  <si>
-    <t>0.9898,0.0053,0.0018,0.0004</t>
-  </si>
-  <si>
-    <t>0.9709,0.0081,0.0019,0.0051</t>
-  </si>
-  <si>
-    <t>0.9853,0.0125,0.0036,0.0004</t>
-  </si>
-  <si>
-    <t>0.9771,0.0110,0.0047,0.0031</t>
-  </si>
-  <si>
-    <t>0.9962,0.0019,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9858,0.0050,0.0002,0.0021</t>
-  </si>
-  <si>
-    <t>0.9816,0.0164,0.0019,0.0008</t>
-  </si>
-  <si>
-    <t>0.0177,0.0143,0.9780,0.0024</t>
-  </si>
-  <si>
-    <t>0.5512,0.0308,0.5594,0.0052</t>
-  </si>
-  <si>
-    <t>0.9257,0.0528,0.0211,0.0040</t>
-  </si>
-  <si>
-    <t>0.0041,0.0041,0.9928,0.0007</t>
-  </si>
-  <si>
-    <t>0.0022,0.0128,0.9913,0.0008</t>
-  </si>
-  <si>
-    <t>0.0055,0.0279,0.9794,0.0033</t>
-  </si>
-  <si>
-    <t>0.0002,0.0012,0.9935,0.0110</t>
-  </si>
-  <si>
-    <t>0.1787,0.0090,0.8632,0.0034</t>
-  </si>
-  <si>
-    <t>0.0017,0.0141,0.9931,0.0014</t>
-  </si>
-  <si>
-    <t>0.0279,0.0100,0.9646,0.0035</t>
-  </si>
-  <si>
-    <t>0.2495,0.3483,0.3825,0.0118</t>
-  </si>
-  <si>
-    <t>0.6772,0.0099,0.4128,0.0116</t>
-  </si>
-  <si>
-    <t>0.8365,0.0073,0.1789,0.0071</t>
-  </si>
-  <si>
-    <t>0.7644,0.0111,0.1825,0.0399</t>
-  </si>
-  <si>
-    <t>0.9835,0.0067,0.0010,0.0021</t>
-  </si>
-  <si>
-    <t>0.9857,0.0030,0.0010,0.0027</t>
-  </si>
-  <si>
-    <t>0.9841,0.0135,0.0037,0.0005</t>
-  </si>
-  <si>
-    <t>0.9748,0.0050,0.0025,0.0081</t>
-  </si>
-  <si>
-    <t>0.9818,0.0031,0.0006,0.0052</t>
-  </si>
-  <si>
-    <t>0.9905,0.0092,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9860,0.0067,0.0010,0.0015</t>
-  </si>
-  <si>
-    <t>0.9811,0.0029,0.0004,0.0055</t>
-  </si>
-  <si>
-    <t>0.1469,0.3968,0.4559,0.0140</t>
-  </si>
-  <si>
-    <t>0.0017,0.0154,0.9926,0.0009</t>
-  </si>
-  <si>
-    <t>0.0057,0.0139,0.9877,0.0008</t>
-  </si>
-  <si>
-    <t>0.1624,0.0183,0.8553,0.0018</t>
-  </si>
-  <si>
-    <t>0.0044,0.0054,0.9795,0.0112</t>
-  </si>
-  <si>
-    <t>0.1078,0.0048,0.4485,0.4573</t>
-  </si>
-  <si>
-    <t>0.0377,0.0285,0.9284,0.0141</t>
-  </si>
-  <si>
-    <t>0.1650,0.0155,0.7392,0.0794</t>
-  </si>
-  <si>
-    <t>0.7828,0.0026,0.0100,0.2214</t>
-  </si>
-  <si>
-    <t>0.0049,0.0307,0.0026,0.9946</t>
-  </si>
-  <si>
-    <t>0.0131,0.0004,0.0004,0.9957</t>
-  </si>
-  <si>
-    <t>0.0071,0.0006,0.0005,0.9968</t>
-  </si>
-  <si>
-    <t>0.0108,0.0001,0.0002,0.9968</t>
-  </si>
-  <si>
-    <t>0.7819,0.0252,0.0061,0.1368</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.5693,0.0948,0.0020,0.1529</t>
+  </si>
+  <si>
+    <t>0.0159,0.0023,0.0014,0.9926</t>
+  </si>
+  <si>
+    <t>0.8427,0.0395,0.0074,0.0508</t>
+  </si>
+  <si>
+    <t>0.1038,0.0080,0.0026,0.9621</t>
+  </si>
+  <si>
+    <t>0.9953,0.0005,0.0000,0.0015</t>
+  </si>
+  <si>
+    <t>0.9935,0.0022,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9861,0.0075,0.0035,0.0010</t>
+  </si>
+  <si>
+    <t>0.9937,0.0014,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9966,0.0006,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9931,0.0074,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9947,0.0013,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9962,0.0005,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.5417,0.0427,0.5534,0.0044</t>
+  </si>
+  <si>
+    <t>0.3063,0.0656,0.6764,0.0064</t>
+  </si>
+  <si>
+    <t>0.1960,0.0048,0.9146,0.0006</t>
+  </si>
+  <si>
+    <t>0.2119,0.0093,0.8497,0.0021</t>
+  </si>
+  <si>
+    <t>0.5768,0.1038,0.3566,0.0152</t>
+  </si>
+  <si>
+    <t>0.0933,0.9278,0.0055,0.0009</t>
+  </si>
+  <si>
+    <t>0.0229,0.9717,0.0027,0.0033</t>
+  </si>
+  <si>
+    <t>0.7451,0.4013,0.0039,0.0028</t>
+  </si>
+  <si>
+    <t>0.2502,0.8892,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.0580,0.9466,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.6726,0.0277,0.3541,0.0190</t>
+  </si>
+  <si>
+    <t>0.2960,0.0075,0.8150,0.0037</t>
+  </si>
+  <si>
+    <t>0.0536,0.0038,0.9570,0.0034</t>
+  </si>
+  <si>
+    <t>0.1420,0.0020,0.9445,0.0006</t>
+  </si>
+  <si>
+    <t>0.0974,0.0047,0.9312,0.0027</t>
+  </si>
+  <si>
+    <t>0.0566,0.0045,0.9338,0.0101</t>
+  </si>
+  <si>
+    <t>0.0006,0.0009,0.9949,0.0033</t>
+  </si>
+  <si>
+    <t>0.9023,0.1297,0.0084,0.0005</t>
+  </si>
+  <si>
+    <t>0.6126,0.1586,0.2946,0.0202</t>
+  </si>
+  <si>
+    <t>0.0067,0.0045,0.9917,0.0004</t>
+  </si>
+  <si>
+    <t>0.1051,0.1588,0.7883,0.0056</t>
+  </si>
+  <si>
+    <t>0.9004,0.0346,0.0332,0.0103</t>
+  </si>
+  <si>
+    <t>0.8491,0.0623,0.0770,0.0130</t>
+  </si>
+  <si>
+    <t>0.8335,0.2823,0.0048,0.0012</t>
+  </si>
+  <si>
+    <t>0.0340,0.9464,0.0359,0.0047</t>
+  </si>
+  <si>
+    <t>0.1967,0.2477,0.6608,0.0698</t>
+  </si>
+  <si>
+    <t>0.0163,0.0277,0.8649,0.1876</t>
+  </si>
+  <si>
+    <t>0.1641,0.0752,0.7333,0.0828</t>
+  </si>
+  <si>
+    <t>0.3846,0.0075,0.7163,0.0139</t>
+  </si>
+  <si>
+    <t>0.0190,0.0209,0.9695,0.0026</t>
+  </si>
+  <si>
+    <t>0.0091,0.9732,0.0104,0.0001</t>
+  </si>
+  <si>
+    <t>0.0168,0.0116,0.9806,0.0015</t>
+  </si>
+  <si>
+    <t>0.0095,0.8296,0.0126,0.6429</t>
+  </si>
+  <si>
+    <t>0.0053,0.9710,0.0555,0.0193</t>
+  </si>
+  <si>
+    <t>0.0035,0.9793,0.0475,0.0030</t>
+  </si>
+  <si>
+    <t>0.0011,0.9943,0.0106,0.0006</t>
+  </si>
+  <si>
+    <t>0.0136,0.1184,0.9335,0.0120</t>
+  </si>
+  <si>
+    <t>0.0009,0.0469,0.9926,0.0011</t>
+  </si>
+  <si>
+    <t>0.0389,0.0024,0.9686,0.0025</t>
+  </si>
+  <si>
+    <t>0.0211,0.0010,0.9808,0.0019</t>
+  </si>
+  <si>
+    <t>0.0007,0.0016,0.9954,0.0034</t>
+  </si>
+  <si>
+    <t>0.0135,0.0163,0.9729,0.0009</t>
+  </si>
+  <si>
+    <t>0.9793,0.0151,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9621,0.0109,0.0358,0.0022</t>
+  </si>
+  <si>
+    <t>0.9532,0.0403,0.0010,0.0041</t>
+  </si>
+  <si>
+    <t>0.0003,0.0023,0.9952,0.0032</t>
+  </si>
+  <si>
+    <t>0.9860,0.0041,0.0003,0.0023</t>
+  </si>
+  <si>
+    <t>0.9873,0.0104,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.9649,0.0462,0.0023,0.0006</t>
+  </si>
+  <si>
+    <t>0.0055,0.6765,0.9334,0.0021</t>
+  </si>
+  <si>
+    <t>0.0083,0.1759,0.9467,0.0105</t>
+  </si>
+  <si>
+    <t>0.0139,0.0897,0.9413,0.0048</t>
+  </si>
+  <si>
+    <t>0.0069,0.8054,0.8346,0.0015</t>
+  </si>
+  <si>
+    <t>0.0015,0.0089,0.9881,0.0046</t>
+  </si>
+  <si>
+    <t>0.0301,0.8362,0.2660,0.0025</t>
+  </si>
+  <si>
+    <t>0.0349,0.9691,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9120,0.0078,0.1381,0.0019</t>
+  </si>
+  <si>
+    <t>0.5230,0.2359,0.3253,0.0056</t>
+  </si>
+  <si>
+    <t>0.0144,0.0459,0.9746,0.0016</t>
+  </si>
+  <si>
+    <t>0.0013,0.8867,0.8725,0.0004</t>
+  </si>
+  <si>
+    <t>0.0082,0.7753,0.4133,0.0001</t>
+  </si>
+  <si>
+    <t>0.0027,0.9603,0.1310,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.9454,0.4642,0.0012</t>
+  </si>
+  <si>
+    <t>0.0548,0.0010,0.0085,0.9660</t>
+  </si>
+  <si>
+    <t>0.0076,0.0038,0.0015,0.9947</t>
+  </si>
+  <si>
+    <t>0.0092,0.0018,0.0015,0.9938</t>
+  </si>
+  <si>
+    <t>0.0130,0.0041,0.0065,0.9900</t>
+  </si>
+  <si>
+    <t>0.0268,0.0151,0.0038,0.9844</t>
+  </si>
+  <si>
+    <t>0.0059,0.0132,0.0004,0.9955</t>
+  </si>
+  <si>
+    <t>0.0018,0.8624,0.8834,0.0003</t>
+  </si>
+  <si>
+    <t>0.0047,0.4972,0.9571,0.0010</t>
+  </si>
+  <si>
+    <t>0.0110,0.3365,0.8898,0.0011</t>
+  </si>
+  <si>
+    <t>0.0052,0.6042,0.9132,0.0028</t>
+  </si>
+  <si>
+    <t>0.0002,0.9701,0.3306,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.8285,0.7920,0.0003</t>
+  </si>
+  <si>
+    <t>0.9948,0.0009,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9826,0.0178,0.0034,0.0005</t>
+  </si>
+  <si>
+    <t>0.9825,0.0231,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.9970,0.0003,0.0000,0.0009</t>
+  </si>
+  <si>
+    <t>0.9816,0.0169,0.0015,0.0009</t>
+  </si>
+  <si>
+    <t>0.9949,0.0025,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9827,0.0162,0.0023,0.0006</t>
+  </si>
+  <si>
+    <t>0.9769,0.0239,0.0027,0.0010</t>
+  </si>
+  <si>
+    <t>0.9967,0.0003,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9947,0.0007,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9936,0.0018,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9972,0.0007,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9966,0.0010,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9973,0.0005,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9932,0.0011,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9959,0.0010,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.0250,0.0036,0.9822,0.0014</t>
+  </si>
+  <si>
+    <t>0.1384,0.0629,0.7966,0.0058</t>
+  </si>
+  <si>
+    <t>0.7095,0.0231,0.1859,0.0657</t>
+  </si>
+  <si>
+    <t>0.1961,0.0035,0.8972,0.0016</t>
+  </si>
+  <si>
+    <t>0.2484,0.7827,0.0076,0.0066</t>
+  </si>
+  <si>
+    <t>0.0746,0.9293,0.0035,0.0004</t>
+  </si>
+  <si>
+    <t>0.0632,0.9129,0.0002,0.0036</t>
+  </si>
+  <si>
+    <t>0.2068,0.8540,0.0033,0.0020</t>
+  </si>
+  <si>
+    <t>0.1346,0.8209,0.0043,0.0347</t>
+  </si>
+  <si>
+    <t>0.0251,0.9710,0.0031,0.0009</t>
+  </si>
+  <si>
+    <t>0.8600,0.1448,0.0261,0.0035</t>
+  </si>
+  <si>
+    <t>0.8198,0.0158,0.0449,0.0523</t>
+  </si>
+  <si>
+    <t>0.1700,0.0072,0.8817,0.0095</t>
+  </si>
+  <si>
+    <t>0.7027,0.0992,0.1282,0.0451</t>
+  </si>
+  <si>
+    <t>0.4097,0.1131,0.4927,0.0288</t>
+  </si>
+  <si>
+    <t>0.0817,0.1742,0.1147,0.8852</t>
+  </si>
+  <si>
+    <t>0.0005,0.9945,0.0179,0.0016</t>
+  </si>
+  <si>
+    <t>0.0021,0.9880,0.0077,0.0061</t>
+  </si>
+  <si>
+    <t>0.0106,0.9684,0.0049,0.0209</t>
+  </si>
+  <si>
+    <t>0.0035,0.9645,0.4891,0.0008</t>
+  </si>
+  <si>
+    <t>0.1033,0.8998,0.0857,0.0017</t>
+  </si>
+  <si>
+    <t>0.7647,0.2598,0.0494,0.0068</t>
+  </si>
+  <si>
+    <t>0.4875,0.6094,0.0314,0.0132</t>
+  </si>
+  <si>
+    <t>0.9844,0.0070,0.0028,0.0017</t>
+  </si>
+  <si>
+    <t>0.9795,0.0156,0.0014,0.0013</t>
+  </si>
+  <si>
+    <t>0.9604,0.0082,0.0040,0.0147</t>
+  </si>
+  <si>
+    <t>0.9752,0.0120,0.0046,0.0021</t>
+  </si>
+  <si>
+    <t>0.9882,0.0016,0.0003,0.0031</t>
+  </si>
+  <si>
+    <t>0.9916,0.0053,0.0032,0.0002</t>
+  </si>
+  <si>
+    <t>0.9854,0.0012,0.0006,0.0052</t>
+  </si>
+  <si>
+    <t>0.9913,0.0009,0.0003,0.0018</t>
+  </si>
+  <si>
+    <t>0.0014,0.5950,0.9547,0.0005</t>
+  </si>
+  <si>
+    <t>0.0086,0.2660,0.9637,0.0018</t>
+  </si>
+  <si>
+    <t>0.0086,0.5075,0.8950,0.0009</t>
+  </si>
+  <si>
+    <t>0.0064,0.3526,0.9170,0.0039</t>
+  </si>
+  <si>
+    <t>0.6406,0.0347,0.1325,0.2152</t>
+  </si>
+  <si>
+    <t>0.4765,0.1959,0.3271,0.0797</t>
+  </si>
+  <si>
+    <t>0.7877,0.0015,0.4343,0.0031</t>
+  </si>
+  <si>
+    <t>0.6457,0.0472,0.3911,0.0123</t>
+  </si>
+  <si>
+    <t>0.0206,0.0046,0.0018,0.9902</t>
+  </si>
+  <si>
+    <t>0.0004,0.0024,0.0041,0.9988</t>
+  </si>
+  <si>
+    <t>0.0003,0.1264,0.0022,0.9967</t>
+  </si>
+  <si>
+    <t>0.0173,0.0031,0.0011,0.9925</t>
+  </si>
+  <si>
+    <t>0.0005,0.7624,0.9651,0.0005</t>
+  </si>
+  <si>
+    <t>0.9434,0.0841,0.0024,0.0012</t>
+  </si>
+  <si>
+    <t>0.1425,0.8810,0.0018,0.0020</t>
+  </si>
+  <si>
+    <t>0.9719,0.0144,0.0024,0.0024</t>
+  </si>
+  <si>
+    <t>0.6551,0.4575,0.0017,0.0036</t>
+  </si>
+  <si>
+    <t>0.9513,0.0097,0.0104,0.0082</t>
+  </si>
+  <si>
+    <t>0.1146,0.0138,0.0027,0.9494</t>
+  </si>
+  <si>
+    <t>0.9029,0.0676,0.0101,0.0187</t>
+  </si>
+  <si>
+    <t>0.0002,0.0596,0.9768,0.0412</t>
+  </si>
+  <si>
+    <t>0.4222,0.0004,0.0043,0.6926</t>
+  </si>
+  <si>
+    <t>0.9484,0.0022,0.0020,0.0325</t>
+  </si>
+  <si>
+    <t>0.7375,0.2107,0.0335,0.0210</t>
+  </si>
+  <si>
+    <t>0.7727,0.1704,0.0515,0.0134</t>
+  </si>
+  <si>
+    <t>0.8950,0.0839,0.0192,0.0050</t>
+  </si>
+  <si>
+    <t>0.1821,0.6118,0.2202,0.0351</t>
+  </si>
+  <si>
+    <t>0.9056,0.0369,0.0420,0.0054</t>
+  </si>
+  <si>
+    <t>0.8966,0.0541,0.0214,0.0082</t>
+  </si>
+  <si>
+    <t>0.9787,0.0077,0.0020,0.0029</t>
+  </si>
+  <si>
+    <t>0.9464,0.0088,0.0025,0.0275</t>
+  </si>
+  <si>
+    <t>0.9931,0.0012,0.0001,0.0013</t>
+  </si>
+  <si>
+    <t>0.9855,0.0009,0.0012,0.0054</t>
+  </si>
+  <si>
+    <t>0.9865,0.0021,0.0006,0.0030</t>
+  </si>
+  <si>
+    <t>0.9841,0.0008,0.0005,0.0099</t>
+  </si>
+  <si>
+    <t>0.9828,0.0065,0.0014,0.0029</t>
+  </si>
+  <si>
+    <t>0.9907,0.0001,0.0001,0.0084</t>
+  </si>
+  <si>
+    <t>0.2959,0.6237,0.0012,0.0151</t>
+  </si>
+  <si>
+    <t>0.8349,0.2540,0.0070,0.0009</t>
+  </si>
+  <si>
+    <t>0.5654,0.5809,0.0073,0.0023</t>
+  </si>
+  <si>
+    <t>0.4032,0.0808,0.6834,0.0121</t>
+  </si>
+  <si>
+    <t>0.7888,0.3223,0.0062,0.0022</t>
+  </si>
+  <si>
+    <t>0.9430,0.0457,0.0035,0.0032</t>
+  </si>
+  <si>
+    <t>0.9815,0.0088,0.0008,0.0017</t>
+  </si>
+  <si>
+    <t>0.9794,0.0092,0.0035,0.0015</t>
+  </si>
+  <si>
+    <t>0.0053,0.0370,0.9869,0.0014</t>
+  </si>
+  <si>
+    <t>0.9764,0.0150,0.0031,0.0015</t>
+  </si>
+  <si>
+    <t>0.0036,0.0098,0.9835,0.0022</t>
+  </si>
+  <si>
+    <t>0.0059,0.1360,0.9747,0.0020</t>
+  </si>
+  <si>
+    <t>0.0495,0.0100,0.9622,0.0006</t>
+  </si>
+  <si>
+    <t>0.0171,0.1152,0.9407,0.0136</t>
+  </si>
+  <si>
+    <t>0.0270,0.0353,0.9599,0.0035</t>
+  </si>
+  <si>
+    <t>0.0423,0.0033,0.9729,0.0006</t>
+  </si>
+  <si>
+    <t>0.0053,0.0056,0.9898,0.0018</t>
+  </si>
+  <si>
+    <t>0.6087,0.0551,0.3562,0.0570</t>
+  </si>
+  <si>
+    <t>0.4429,0.0171,0.6370,0.0164</t>
+  </si>
+  <si>
+    <t>0.7071,0.1048,0.1597,0.0180</t>
+  </si>
+  <si>
+    <t>0.5424,0.0716,0.4574,0.0029</t>
+  </si>
+  <si>
+    <t>0.1513,0.6046,0.2882,0.0191</t>
+  </si>
+  <si>
+    <t>0.6345,0.0338,0.4480,0.0026</t>
+  </si>
+  <si>
+    <t>0.7399,0.0228,0.2267,0.0200</t>
+  </si>
+  <si>
+    <t>0.3834,0.1021,0.5705,0.0096</t>
+  </si>
+  <si>
+    <t>0.7258,0.3142,0.0386,0.0086</t>
+  </si>
+  <si>
+    <t>0.9575,0.1008,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9168,0.1499,0.0020,0.0006</t>
+  </si>
+  <si>
+    <t>0.9125,0.1561,0.0019,0.0006</t>
+  </si>
+  <si>
+    <t>0.9435,0.0497,0.0036,0.0046</t>
+  </si>
+  <si>
+    <t>0.7763,0.0075,0.2341,0.0146</t>
+  </si>
+  <si>
+    <t>0.5824,0.0115,0.4019,0.0595</t>
+  </si>
+  <si>
+    <t>0.4258,0.0387,0.1262,0.4410</t>
+  </si>
+  <si>
+    <t>0.5715,0.0225,0.4325,0.0402</t>
+  </si>
+  <si>
+    <t>0.7044,0.0221,0.3280,0.0114</t>
+  </si>
+  <si>
+    <t>0.0486,0.0410,0.8730,0.0947</t>
+  </si>
+  <si>
+    <t>0.0749,0.0331,0.8982,0.0166</t>
+  </si>
+  <si>
+    <t>0.0539,0.0767,0.9077,0.0052</t>
+  </si>
+  <si>
+    <t>0.0395,0.0323,0.8988,0.0341</t>
+  </si>
+  <si>
+    <t>0.0309,0.0391,0.9427,0.0013</t>
+  </si>
+  <si>
+    <t>0.9824,0.0093,0.0005,0.0015</t>
+  </si>
+  <si>
+    <t>0.9753,0.0218,0.0008,0.0014</t>
+  </si>
+  <si>
+    <t>0.9959,0.0008,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9850,0.0121,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9926,0.0016,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9947,0.0011,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9941,0.0016,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9865,0.0070,0.0009,0.0010</t>
+  </si>
+  <si>
+    <t>0.1381,0.0158,0.8952,0.0021</t>
+  </si>
+  <si>
+    <t>0.3628,0.1397,0.5954,0.0047</t>
+  </si>
+  <si>
+    <t>0.8613,0.0366,0.1043,0.0085</t>
+  </si>
+  <si>
+    <t>0.0082,0.0091,0.9886,0.0004</t>
+  </si>
+  <si>
+    <t>0.0012,0.1354,0.9836,0.0002</t>
+  </si>
+  <si>
+    <t>0.0097,0.0351,0.9814,0.0010</t>
+  </si>
+  <si>
+    <t>0.0010,0.0036,0.9969,0.0005</t>
+  </si>
+  <si>
+    <t>0.0134,0.0563,0.9464,0.0036</t>
+  </si>
+  <si>
+    <t>0.0180,0.0265,0.9807,0.0012</t>
+  </si>
+  <si>
+    <t>0.0501,0.0349,0.9314,0.0095</t>
+  </si>
+  <si>
+    <t>0.0729,0.6458,0.3639,0.0068</t>
+  </si>
+  <si>
+    <t>0.6185,0.0111,0.4544,0.0203</t>
+  </si>
+  <si>
+    <t>0.4032,0.0157,0.7461,0.0022</t>
+  </si>
+  <si>
+    <t>0.8801,0.0009,0.1617,0.0037</t>
+  </si>
+  <si>
+    <t>0.9771,0.0153,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9923,0.0046,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9883,0.0081,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.9683,0.0394,0.0039,0.0006</t>
+  </si>
+  <si>
+    <t>0.9737,0.0066,0.0005,0.0056</t>
+  </si>
+  <si>
+    <t>0.9885,0.0031,0.0001,0.0019</t>
+  </si>
+  <si>
+    <t>0.9921,0.0030,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9932,0.0038,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0132,0.0198,0.9774,0.0009</t>
+  </si>
+  <si>
+    <t>0.0015,0.1195,0.9889,0.0002</t>
+  </si>
+  <si>
+    <t>0.0024,0.2760,0.9615,0.0011</t>
+  </si>
+  <si>
+    <t>0.0338,0.3081,0.5729,0.0008</t>
+  </si>
+  <si>
+    <t>0.0061,0.0048,0.9816,0.0077</t>
+  </si>
+  <si>
+    <t>0.0185,0.0216,0.9179,0.0822</t>
+  </si>
+  <si>
+    <t>0.0990,0.1414,0.8178,0.0285</t>
+  </si>
+  <si>
+    <t>0.0787,0.1082,0.7269,0.1387</t>
+  </si>
+  <si>
+    <t>0.7524,0.0012,0.0014,0.3845</t>
+  </si>
+  <si>
+    <t>0.0184,0.1150,0.0065,0.9780</t>
+  </si>
+  <si>
+    <t>0.0720,0.0008,0.0021,0.9721</t>
+  </si>
+  <si>
+    <t>0.0060,0.0002,0.0006,0.9971</t>
+  </si>
+  <si>
+    <t>0.0055,0.0006,0.0006,0.9970</t>
+  </si>
+  <si>
+    <t>0.3927,0.2560,0.0300,0.4963</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,10 +2133,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,10 +2231,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,10 +2413,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2458,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,10 +2819,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,10 +2889,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,10 +2973,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,10 +2987,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3004,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,10 +3113,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3130,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,10 +3141,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3158,7 @@
         <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3592,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,10 +3673,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3718,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3841,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3855,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,10 +3869,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,10 +3911,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3928,7 @@
         <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4093,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,10 +4135,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4166,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4208,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4359,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,10 +4597,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4670,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4684,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4695,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,10 +4709,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4726,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4765,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,10 +4807,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4824,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,10 +4905,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,7 +5048,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,10 +5171,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,10 +5339,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5521,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
